--- a/docs/DesignDocumentSample.xlsx
+++ b/docs/DesignDocumentSample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\other\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49974F21-D1EB-45FE-9D42-36DC77C3CFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085EAA04-1BEE-4118-BD95-C295AF35F73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,10 +853,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>TrnTerminal</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>端末マスタ</t>
     <rPh sb="0" eb="2">
       <t>タンマツ</t>
@@ -965,6 +961,10 @@
     <rPh sb="0" eb="2">
       <t>ビコウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MstTerminal</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1579,60 +1579,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1721,6 +1667,60 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3182,13 +3182,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>100854</xdr:colOff>
+      <xdr:colOff>61773</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>39220</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>84886</xdr:rowOff>
     </xdr:to>
@@ -3208,8 +3208,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="1206501" y="2033867"/>
-          <a:ext cx="451971" cy="389313"/>
+          <a:off x="882388" y="1929566"/>
+          <a:ext cx="485304" cy="387589"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -4018,14 +4018,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>234458</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>11202</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>100853</xdr:colOff>
+      <xdr:colOff>61773</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>67235</xdr:rowOff>
     </xdr:to>
@@ -4042,8 +4042,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="552824" y="1662202"/>
-          <a:ext cx="653676" cy="743327"/>
+          <a:off x="234458" y="1559625"/>
+          <a:ext cx="647930" cy="739879"/>
         </a:xfrm>
         <a:prstGeom prst="can">
           <a:avLst>
@@ -4500,7 +4500,7 @@
         <a:prstGeom prst="bentConnector4">
           <a:avLst>
             <a:gd name="adj1" fmla="val 33423"/>
-            <a:gd name="adj2" fmla="val 136885"/>
+            <a:gd name="adj2" fmla="val 134979"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln w="12700">
@@ -4582,8 +4582,8 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>-1</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>273538</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>15125</xdr:rowOff>
     </xdr:from>
@@ -5034,8 +5034,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6984068" y="1520075"/>
-          <a:ext cx="1514474" cy="716056"/>
+          <a:off x="6916905" y="1563548"/>
+          <a:ext cx="1501041" cy="676002"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartPredefinedProcess">
           <a:avLst/>
@@ -10258,109 +10258,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="63" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="89" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="51" t="s">
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="53" t="s">
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54"/>
-      <c r="W1" s="54"/>
-      <c r="X1" s="54"/>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54"/>
-      <c r="AA1" s="54"/>
-      <c r="AB1" s="54"/>
-      <c r="AC1" s="54"/>
-      <c r="AD1" s="55"/>
-      <c r="AE1" s="51" t="s">
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="80"/>
+      <c r="V1" s="80"/>
+      <c r="W1" s="80"/>
+      <c r="X1" s="80"/>
+      <c r="Y1" s="80"/>
+      <c r="Z1" s="80"/>
+      <c r="AA1" s="80"/>
+      <c r="AB1" s="80"/>
+      <c r="AC1" s="80"/>
+      <c r="AD1" s="81"/>
+      <c r="AE1" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="51"/>
-      <c r="AG1" s="60"/>
-      <c r="AH1" s="60"/>
-      <c r="AI1" s="60"/>
-      <c r="AJ1" s="51" t="s">
+      <c r="AF1" s="77"/>
+      <c r="AG1" s="86"/>
+      <c r="AH1" s="86"/>
+      <c r="AI1" s="86"/>
+      <c r="AJ1" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="47"/>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="48"/>
+      <c r="AK1" s="77"/>
+      <c r="AL1" s="91"/>
+      <c r="AM1" s="91"/>
+      <c r="AN1" s="92"/>
       <c r="AO1" s="1"/>
     </row>
     <row r="2" spans="1:41" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="64" t="s">
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="Y2" s="57"/>
-      <c r="Z2" s="57"/>
-      <c r="AA2" s="57"/>
-      <c r="AB2" s="57"/>
-      <c r="AC2" s="57"/>
-      <c r="AD2" s="58"/>
-      <c r="AE2" s="52" t="s">
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="83"/>
+      <c r="T2" s="83"/>
+      <c r="U2" s="83"/>
+      <c r="V2" s="83"/>
+      <c r="W2" s="83"/>
+      <c r="X2" s="83"/>
+      <c r="Y2" s="83"/>
+      <c r="Z2" s="83"/>
+      <c r="AA2" s="83"/>
+      <c r="AB2" s="83"/>
+      <c r="AC2" s="83"/>
+      <c r="AD2" s="84"/>
+      <c r="AE2" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="AF2" s="52"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="52" t="s">
+      <c r="AF2" s="78"/>
+      <c r="AG2" s="87"/>
+      <c r="AH2" s="87"/>
+      <c r="AI2" s="87"/>
+      <c r="AJ2" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="49"/>
-      <c r="AM2" s="49"/>
-      <c r="AN2" s="50"/>
+      <c r="AK2" s="78"/>
+      <c r="AL2" s="93"/>
+      <c r="AM2" s="93"/>
+      <c r="AN2" s="94"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -10860,72 +10860,72 @@
     </row>
     <row r="17" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="85"/>
-      <c r="O17" s="65" t="s">
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="67"/>
+      <c r="O17" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="66"/>
-      <c r="T17" s="66"/>
-      <c r="U17" s="66"/>
-      <c r="V17" s="66"/>
-      <c r="W17" s="66"/>
-      <c r="X17" s="67"/>
-      <c r="AC17" s="71" t="s">
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="48"/>
+      <c r="U17" s="48"/>
+      <c r="V17" s="48"/>
+      <c r="W17" s="48"/>
+      <c r="X17" s="49"/>
+      <c r="AC17" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="AD17" s="72"/>
-      <c r="AE17" s="72"/>
-      <c r="AF17" s="72"/>
-      <c r="AG17" s="72"/>
-      <c r="AH17" s="72"/>
-      <c r="AI17" s="72"/>
-      <c r="AJ17" s="72"/>
-      <c r="AK17" s="72"/>
-      <c r="AL17" s="73"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="54"/>
+      <c r="AF17" s="54"/>
+      <c r="AG17" s="54"/>
+      <c r="AH17" s="54"/>
+      <c r="AI17" s="54"/>
+      <c r="AJ17" s="54"/>
+      <c r="AK17" s="54"/>
+      <c r="AL17" s="55"/>
       <c r="AN17" s="3"/>
     </row>
     <row r="18" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="87"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="87"/>
-      <c r="I18" s="87"/>
-      <c r="J18" s="88"/>
-      <c r="O18" s="68"/>
-      <c r="P18" s="69"/>
-      <c r="Q18" s="69"/>
-      <c r="R18" s="69"/>
-      <c r="S18" s="69"/>
-      <c r="T18" s="69"/>
-      <c r="U18" s="69"/>
-      <c r="V18" s="69"/>
-      <c r="W18" s="69"/>
-      <c r="X18" s="70"/>
-      <c r="AC18" s="74"/>
-      <c r="AD18" s="75"/>
-      <c r="AE18" s="75"/>
-      <c r="AF18" s="75"/>
-      <c r="AG18" s="75"/>
-      <c r="AH18" s="75"/>
-      <c r="AI18" s="75"/>
-      <c r="AJ18" s="75"/>
-      <c r="AK18" s="75"/>
-      <c r="AL18" s="76"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="70"/>
+      <c r="O18" s="50"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="51"/>
+      <c r="R18" s="51"/>
+      <c r="S18" s="51"/>
+      <c r="T18" s="51"/>
+      <c r="U18" s="51"/>
+      <c r="V18" s="51"/>
+      <c r="W18" s="51"/>
+      <c r="X18" s="52"/>
+      <c r="AC18" s="56"/>
+      <c r="AD18" s="57"/>
+      <c r="AE18" s="57"/>
+      <c r="AF18" s="57"/>
+      <c r="AG18" s="57"/>
+      <c r="AH18" s="57"/>
+      <c r="AI18" s="57"/>
+      <c r="AJ18" s="57"/>
+      <c r="AK18" s="57"/>
+      <c r="AL18" s="58"/>
       <c r="AN18" s="3"/>
     </row>
     <row r="19" spans="1:40" x14ac:dyDescent="0.3">
@@ -11040,12 +11040,12 @@
       <c r="A22" s="2"/>
       <c r="C22" s="7"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="89" t="s">
+      <c r="E22" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="91"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="73"/>
       <c r="I22" s="8"/>
       <c r="J22" s="9"/>
       <c r="O22" s="13"/>
@@ -11074,10 +11074,10 @@
       <c r="A23" s="2"/>
       <c r="C23" s="7"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="94"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="76"/>
       <c r="I23" s="8"/>
       <c r="J23" s="9"/>
       <c r="O23" s="13"/>
@@ -11128,18 +11128,18 @@
       <c r="V24" s="14"/>
       <c r="W24" s="14"/>
       <c r="X24" s="15"/>
-      <c r="AC24" s="77" t="s">
+      <c r="AC24" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="AD24" s="78"/>
-      <c r="AE24" s="78"/>
-      <c r="AF24" s="78"/>
-      <c r="AG24" s="78"/>
-      <c r="AH24" s="78"/>
-      <c r="AI24" s="78"/>
-      <c r="AJ24" s="78"/>
-      <c r="AK24" s="78"/>
-      <c r="AL24" s="79"/>
+      <c r="AD24" s="60"/>
+      <c r="AE24" s="60"/>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="61"/>
       <c r="AN24" s="3"/>
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.3">
@@ -11166,16 +11166,16 @@
       <c r="V25" s="14"/>
       <c r="W25" s="14"/>
       <c r="X25" s="15"/>
-      <c r="AC25" s="80"/>
-      <c r="AD25" s="81"/>
-      <c r="AE25" s="81"/>
-      <c r="AF25" s="81"/>
-      <c r="AG25" s="81"/>
-      <c r="AH25" s="81"/>
-      <c r="AI25" s="81"/>
-      <c r="AJ25" s="81"/>
-      <c r="AK25" s="81"/>
-      <c r="AL25" s="82"/>
+      <c r="AC25" s="62"/>
+      <c r="AD25" s="63"/>
+      <c r="AE25" s="63"/>
+      <c r="AF25" s="63"/>
+      <c r="AG25" s="63"/>
+      <c r="AH25" s="63"/>
+      <c r="AI25" s="63"/>
+      <c r="AJ25" s="63"/>
+      <c r="AK25" s="63"/>
+      <c r="AL25" s="64"/>
       <c r="AN25" s="3"/>
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.3">
@@ -11338,18 +11338,18 @@
     </row>
     <row r="31" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
-      <c r="O31" s="65" t="s">
+      <c r="O31" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="66"/>
-      <c r="R31" s="66"/>
-      <c r="S31" s="66"/>
-      <c r="T31" s="66"/>
-      <c r="U31" s="66"/>
-      <c r="V31" s="66"/>
-      <c r="W31" s="66"/>
-      <c r="X31" s="67"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="48"/>
+      <c r="R31" s="48"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="48"/>
+      <c r="U31" s="48"/>
+      <c r="V31" s="48"/>
+      <c r="W31" s="48"/>
+      <c r="X31" s="49"/>
       <c r="AC31" s="19"/>
       <c r="AD31" s="20" t="s">
         <v>24</v>
@@ -11366,16 +11366,16 @@
     </row>
     <row r="32" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
-      <c r="O32" s="68"/>
-      <c r="P32" s="69"/>
-      <c r="Q32" s="69"/>
-      <c r="R32" s="69"/>
-      <c r="S32" s="69"/>
-      <c r="T32" s="69"/>
-      <c r="U32" s="69"/>
-      <c r="V32" s="69"/>
-      <c r="W32" s="69"/>
-      <c r="X32" s="70"/>
+      <c r="O32" s="50"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="51"/>
+      <c r="R32" s="51"/>
+      <c r="S32" s="51"/>
+      <c r="T32" s="51"/>
+      <c r="U32" s="51"/>
+      <c r="V32" s="51"/>
+      <c r="W32" s="51"/>
+      <c r="X32" s="52"/>
       <c r="AC32" s="19"/>
       <c r="AD32" s="20" t="s">
         <v>25</v>
@@ -11643,12 +11643,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="O17:X18"/>
-    <mergeCell ref="O31:X32"/>
-    <mergeCell ref="AC17:AL18"/>
-    <mergeCell ref="AC24:AL25"/>
-    <mergeCell ref="C17:J18"/>
-    <mergeCell ref="E22:H23"/>
+    <mergeCell ref="AL1:AN1"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="AE1:AF1"/>
     <mergeCell ref="J1:M2"/>
     <mergeCell ref="N1:AD2"/>
     <mergeCell ref="A1:D1"/>
@@ -11658,11 +11657,12 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="E2:I2"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="O17:X18"/>
+    <mergeCell ref="O31:X32"/>
+    <mergeCell ref="AC17:AL18"/>
+    <mergeCell ref="AC24:AL25"/>
+    <mergeCell ref="C17:J18"/>
+    <mergeCell ref="E22:H23"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.35433070866141736" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -12125,7 +12125,7 @@
     <row r="44" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -13162,7 +13162,7 @@
       <c r="G4" s="45"/>
       <c r="H4" s="45"/>
       <c r="I4" s="44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -13668,10 +13668,10 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="B24" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="C24" s="44">
         <v>1</v>
@@ -13697,10 +13697,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="B25" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="C25" s="44">
         <v>2</v>
@@ -13724,16 +13724,16 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="B26" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="C26" s="44">
         <v>3</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E26" s="44" t="s">
         <v>70</v>
@@ -13744,21 +13744,21 @@
       <c r="G26" s="45"/>
       <c r="H26" s="45"/>
       <c r="I26" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="B27" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="C27" s="44">
         <v>4</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E27" s="44" t="s">
         <v>70</v>
@@ -13769,15 +13769,15 @@
       <c r="G27" s="45"/>
       <c r="H27" s="45"/>
       <c r="I27" s="44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="B28" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="C28" s="44">
         <v>7</v>
@@ -13799,10 +13799,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="B29" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="C29" s="44">
         <v>8</v>
@@ -13826,10 +13826,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="B30" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="C30" s="44">
         <v>9</v>
@@ -13853,10 +13853,10 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="B31" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="C31" s="44">
         <v>10</v>
@@ -13880,10 +13880,10 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="B32" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="C32" s="44">
         <v>11</v>
@@ -13954,7 +13954,7 @@
       <c r="G34" s="45"/>
       <c r="H34" s="45"/>
       <c r="I34" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -13979,7 +13979,7 @@
       <c r="G35" s="45"/>
       <c r="H35" s="45"/>
       <c r="I35" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="H41" s="45"/>
       <c r="I41" s="44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="H42" s="45"/>
       <c r="I42" s="44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="H43" s="45"/>
       <c r="I43" s="44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="H44" s="45"/>
       <c r="I44" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
@@ -14241,7 +14241,7 @@
       <c r="G45" s="45"/>
       <c r="H45" s="45"/>
       <c r="I45" s="44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -14266,7 +14266,7 @@
       <c r="G46" s="45"/>
       <c r="H46" s="45"/>
       <c r="I46" s="44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
@@ -14482,12 +14482,12 @@
   </sheetData>
   <autoFilter ref="A1:I54" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:B17 A19:B32 A34:B54">
+  <conditionalFormatting sqref="A2:B17 A34:B54 A19:B32">
     <cfRule type="expression" dxfId="18" priority="16">
       <formula>$A2=$A1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B33 A33:A39">
+  <conditionalFormatting sqref="A2:B33 A24:A39">
     <cfRule type="expression" dxfId="17" priority="18">
       <formula>$A2=#REF!</formula>
     </cfRule>
@@ -14512,12 +14512,12 @@
       <formula>$A33&lt;&gt;$A12</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:I2 A2:A16 A3:B12 C4:I4 C6 C8:I8 C10 C12 A13:I13 B13:B16 A14:B32 C15:I15 C17 C19:I19 C21 C23 A24:I24 A33:H33 A33:A39">
+  <conditionalFormatting sqref="A2:I2 A2:A16 A3:B12 C4:I4 C6 C8:I8 C10 C12 A13:I13 B13:B16 A14:B32 C15:I15 C17 C19:I19 C21 C23 A24:I24 A33:H33 A24:A39">
     <cfRule type="expression" dxfId="12" priority="19">
       <formula>$A2&lt;&gt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:I15 A16:B17 D16:I17 C16:C23 A19:B23 D19:I23 A24:I32 A34:I54">
+  <conditionalFormatting sqref="A2:I15 A16:B17 D16:I17 C16:C23 A19:B23 D19:I23 A34:I54 A24:I32">
     <cfRule type="expression" dxfId="11" priority="15">
       <formula>$A2&lt;&gt;$A1</formula>
     </cfRule>
